--- a/data/Mirror.xlsx
+++ b/data/Mirror.xlsx
@@ -433,52 +433,9 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>fk:BaseScene</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>fk:World</t>
-        </is>
-      </c>
-    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
